--- a/deploy/src/main/resources/TRACK-FAIL-TEMPLATE.xlsx
+++ b/deploy/src/main/resources/TRACK-FAIL-TEMPLATE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yangxu\IdeaProjects\forward\deploy\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{754539F5-BD83-4F80-AF35-2F61812AB07C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C4A54DB-F34A-4A2E-AD8E-DD313F62E91B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-33017" yWindow="-103" windowWidth="33120" windowHeight="18120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -84,11 +84,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>接口名称
-（埋点平台包含服务端时，必填）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>触发时机（必填）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -202,6 +197,11 @@
 8.除了标注为可多选外，其他必填项都为单选。
 9.埋点位置说明 导入 产研系统埋点事件“备注”字段。</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>接口名称
+（埋点平台含服务端时，必填；不含服务端，该字段不显示）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -785,10 +785,10 @@
     </row>
     <row r="2" spans="1:17" ht="176.55" customHeight="1">
       <c r="A2" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C2" s="12"/>
       <c r="D2" s="12"/>
@@ -806,9 +806,9 @@
       <c r="P2" s="12"/>
       <c r="Q2" s="12"/>
     </row>
-    <row r="3" spans="1:17" ht="46.8">
+    <row r="3" spans="1:17" ht="62.4">
       <c r="A3" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>1</v>
@@ -847,16 +847,16 @@
         <v>12</v>
       </c>
       <c r="N3" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="P3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="Q3" s="2" t="s">
         <v>14</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/deploy/src/main/resources/TRACK-FAIL-TEMPLATE.xlsx
+++ b/deploy/src/main/resources/TRACK-FAIL-TEMPLATE.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25427"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yangxu\IdeaProjects\forward\deploy\src\main\resources\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C4A54DB-F34A-4A2E-AD8E-DD313F62E91B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-33017" yWindow="-103" windowWidth="33120" windowHeight="18120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="28800" windowHeight="12540"/>
   </bookViews>
   <sheets>
     <sheet name="校验结果" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
@@ -23,103 +17,9 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>新增埋点事件说明</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>序号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>一级分类（必填）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>二级分类（必填）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">三级分类（必填）
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="冬青黑体简体中文 W3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>若需要添加请联系PMO</t>
-    </r>
-  </si>
-  <si>
-    <t>四级分类（必填）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>五级分类</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>事件中文名（必填）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>事件英文名（必填）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>属性中文名（必填）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>属性英文名（必填）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>数据类型（必填）</t>
-  </si>
-  <si>
-    <t>埋点平台（必填，可多选）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>触发时机（必填）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>埋点所属环境（必填）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>错误信息</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>导入时，请删除“错误信息”列</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="0"/>
-        <rFont val="冬青黑体简体中文 W3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>埋点位置说明</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="冬青黑体简体中文 W3"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-（埋点平台含非服务端时，必填。可填写PRD或者wiki链接）</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -195,34 +95,122 @@
 6.在填写“埋点平台”字段时，请严格按照示例1中所示枚举值填写，如该事件需要在安卓端和 iOS 端进行埋点，请填写：“Android/iOS”，除 Android、iOS、JavaScript、小程序、服务端之外，请填写“其他”。
 7.埋点所属环境，多选，选择项：测试环境、模拟环境、生产环境。若需要在多个环境埋点，请用“/”隔开。
 8.除了标注为可多选外，其他必填项都为单选。
-9.埋点位置说明 导入 产研系统埋点事件“备注”字段。</t>
+9.埋点位置说明 导入 产研系统埋点事件“备注”字段。
+10.对于带有“$”符号的属性为预置属性不可进行修改。</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>错误信息</t>
+  </si>
+  <si>
+    <t>序号</t>
+  </si>
+  <si>
+    <t>一级分类（必填）</t>
+  </si>
+  <si>
+    <t>二级分类（必填）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="冬青黑体简体中文 W3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">三级分类（必填）
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="冬青黑体简体中文 W3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>若需要添加请联系PMO</t>
+    </r>
+  </si>
+  <si>
+    <t>四级分类（必填）</t>
+  </si>
+  <si>
+    <t>五级分类</t>
+  </si>
+  <si>
+    <t>事件中文名（必填）</t>
+  </si>
+  <si>
+    <t>事件英文名（必填）</t>
+  </si>
+  <si>
+    <t>属性中文名（必填）</t>
+  </si>
+  <si>
+    <t>属性英文名（必填）</t>
+  </si>
+  <si>
+    <t>数据类型（必填）</t>
+  </si>
+  <si>
+    <t>埋点平台（必填，可多选）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="冬青黑体简体中文 W3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>埋点位置说明</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="冬青黑体简体中文 W3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+（埋点平台含非服务端时，必填。可填写PRD或者wiki链接）</t>
+    </r>
   </si>
   <si>
     <t>接口名称
 （埋点平台含服务端时，必填；不含服务端，该字段不显示）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>触发时机（必填）</t>
+  </si>
+  <si>
+    <t>埋点所属环境（必填）</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="冬青黑体简体中文 W3"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
@@ -232,7 +220,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color indexed="8"/>
+      <color rgb="FFFF0000"/>
       <name val="冬青黑体简体中文 W3"/>
       <charset val="134"/>
     </font>
@@ -245,6 +233,163 @@
     </font>
     <font>
       <sz val="12"/>
+      <color theme="0"/>
+      <name val="冬青黑体简体中文 W3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color rgb="FF565656"/>
       <name val="冬青黑体简体中文 W3"/>
       <charset val="134"/>
@@ -262,25 +407,13 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="冬青黑体简体中文 W3"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="冬青黑体简体中文 W3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="冬青黑体简体中文 W3"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -289,18 +422,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28B27B"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFEF1C8"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -311,8 +444,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -322,14 +641,14 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="0" tint="-0.1498764000366222"/>
+        <color theme="0" tint="-0.149876400036622"/>
       </left>
       <right/>
       <top style="thin">
-        <color theme="0" tint="-0.1498764000366222"/>
+        <color theme="0" tint="-0.149876400036622"/>
       </top>
       <bottom style="thin">
-        <color theme="0" tint="-0.1498764000366222"/>
+        <color theme="0" tint="-0.149876400036622"/>
       </bottom>
       <diagonal/>
     </border>
@@ -337,10 +656,10 @@
       <left/>
       <right/>
       <top style="thin">
-        <color theme="0" tint="-0.1498764000366222"/>
+        <color theme="0" tint="-0.149876400036622"/>
       </top>
       <bottom style="thin">
-        <color theme="0" tint="-0.1498764000366222"/>
+        <color theme="0" tint="-0.149876400036622"/>
       </bottom>
       <diagonal/>
     </border>
@@ -350,7 +669,7 @@
       </left>
       <right/>
       <top style="thin">
-        <color theme="0" tint="-0.1498764000366222"/>
+        <color theme="0" tint="-0.149876400036622"/>
       </top>
       <bottom style="thin">
         <color rgb="FFDBDBDB"/>
@@ -361,7 +680,7 @@
       <left/>
       <right/>
       <top style="thin">
-        <color theme="0" tint="-0.1498764000366222"/>
+        <color theme="0" tint="-0.149876400036622"/>
       </top>
       <bottom style="thin">
         <color rgb="FFDBDBDB"/>
@@ -381,9 +700,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -391,56 +952,100 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
+    <cellStyle name="输入" xfId="3" builtinId="20"/>
+    <cellStyle name="货币" xfId="4" builtinId="4"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
+    <cellStyle name="差" xfId="7" builtinId="27"/>
+    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
+    <cellStyle name="超链接" xfId="10" builtinId="8"/>
+    <cellStyle name="百分比" xfId="11" builtinId="5"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
+    <cellStyle name="标题" xfId="17" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
+    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="计算" xfId="25" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
+    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
+    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
+    <cellStyle name="汇总" xfId="30" builtinId="25"/>
+    <cellStyle name="好" xfId="31" builtinId="26"/>
+    <cellStyle name="适中" xfId="32" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
+    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
+    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
+    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
+    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -489,7 +1094,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -522,26 +1127,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -574,23 +1162,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -732,131 +1303,126 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1BA069B-B6F2-4DD1-938D-C7528A885D0A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:Q3"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="2"/>
   <cols>
-    <col min="1" max="1" width="46.6640625" customWidth="1"/>
-    <col min="2" max="2" width="6.44140625" customWidth="1"/>
-    <col min="3" max="3" width="17.21875" customWidth="1"/>
-    <col min="4" max="4" width="16.33203125" customWidth="1"/>
-    <col min="5" max="5" width="19.109375" customWidth="1"/>
-    <col min="6" max="6" width="16.109375" customWidth="1"/>
-    <col min="7" max="7" width="13.88671875" customWidth="1"/>
-    <col min="8" max="8" width="25.77734375" customWidth="1"/>
-    <col min="9" max="10" width="19.77734375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.77734375" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="30.44140625" customWidth="1"/>
-    <col min="16" max="16" width="26.44140625" customWidth="1"/>
-    <col min="17" max="17" width="33.88671875" customWidth="1"/>
+    <col min="1" max="1" width="46.6666666666667" customWidth="1"/>
+    <col min="2" max="2" width="6.44166666666667" customWidth="1"/>
+    <col min="3" max="3" width="17.2166666666667" customWidth="1"/>
+    <col min="4" max="4" width="16.3333333333333" customWidth="1"/>
+    <col min="5" max="5" width="19.1083333333333" customWidth="1"/>
+    <col min="6" max="6" width="16.1083333333333" customWidth="1"/>
+    <col min="7" max="7" width="13.8833333333333" customWidth="1"/>
+    <col min="8" max="8" width="25.775" customWidth="1"/>
+    <col min="9" max="10" width="19.775" customWidth="1"/>
+    <col min="11" max="11" width="25.1083333333333" customWidth="1"/>
+    <col min="12" max="12" width="17.775" customWidth="1"/>
+    <col min="13" max="15" width="30.4416666666667" customWidth="1"/>
+    <col min="16" max="16" width="26.4416666666667" customWidth="1"/>
+    <col min="17" max="17" width="33.8833333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.6">
+    <row r="1" spans="1:17">
       <c r="A1" s="1"/>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="10"/>
-      <c r="O1" s="10"/>
-      <c r="P1" s="10"/>
-      <c r="Q1" s="10"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
     </row>
-    <row r="2" spans="1:17" ht="176.55" customHeight="1">
-      <c r="A2" s="7" t="s">
+    <row r="2" ht="176.55" customHeight="1" spans="1:17">
+      <c r="A2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+    </row>
+    <row r="3" ht="42.75" spans="1:17">
+      <c r="A3" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K3" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="M3" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="N3" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="O3" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="P3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-      <c r="L2" s="12"/>
-      <c r="M2" s="12"/>
-      <c r="N2" s="12"/>
-      <c r="O2" s="12"/>
-      <c r="P2" s="12"/>
-      <c r="Q2" s="12"/>
-    </row>
-    <row r="3" spans="1:17" ht="62.4">
-      <c r="A3" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="N3" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="O3" s="5" t="s">
+      <c r="Q3" s="8" t="s">
         <v>19</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -864,8 +1430,8 @@
     <mergeCell ref="B1:Q1"/>
     <mergeCell ref="B2:Q2"/>
   </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>